--- a/tools/_out/groupB_20261021/out/af/DesignTable_6805_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/af/DesignTable_6805_SW2.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>N1 printed 0.63 both passes (non-FG prints 1.02; a 3/8-18 female leg ~1.02) - as-printed, likely typo | Air-Way N1 0.63 cannot be built (female -06 port MS51503 P1 0.68 is longer than the leg) -&gt; Brennan CAD record N 1.02 (= Air-Way's own non-FG 6805-08-06-NWO row; user Q1 2026-10-20 "use brennans") | leg 1: adjustable ORB tip-to-body-face 0.86 = Air-Way 6801 ORB_I3 for -08 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.344 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 0.66 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
+          <t>N1 printed 0.63 both passes (non-FG prints 1.02; a 3/8-18 female leg ~1.02) - as-printed, likely typo | Air-Way N1 0.63 cannot be built (female -06 port MS51503 P1 0.68 is longer than the leg) -&gt; Brennan CAD record N 1.02 (= Air-Way's own non-FG 6805-08-06-NWO row; user Q1 2026-10-20 "use brennans", confirmed 2026-10-21) | leg 1: adjustable ORB tip-to-body-face 0.86 = Air-Way 6801 ORB_I3 for -08 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.344 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 0.66 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
